--- a/ig/DM-37/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -318,13 +318,13 @@
     <t>098</t>
   </si>
   <si>
-    <t>Bassin thérapeutique pour balnéothérapie (&lt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&lt;25m2)</t>
   </si>
   <si>
     <t>099</t>
   </si>
   <si>
-    <t>Piscine pour balnéothérapie (&gt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&gt;=25m2)</t>
   </si>
   <si>
     <t>100</t>
@@ -943,6 +943,18 @@
   </si>
   <si>
     <t>Arthromoteurs membres supérieurs (épaules, coudes)</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>Salle hybride</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Vidéo assistance</t>
   </si>
   <si>
     <t/>
@@ -1221,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B143"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2361,15 +2373,31 @@
         <v>310</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
